--- a/XLibur.Tests/Resource/Other/Pictures/ImageShapeZOrder-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/Pictures/ImageShapeZOrder-Output.xlsx
@@ -521,19 +521,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData/>
-  <x:phoneticPr fontId="1"/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:drawing r:id="rId1"/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/Pictures/ImageShapeZOrder-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/Pictures/ImageShapeZOrder-Output.xlsx
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -161,37 +161,56 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5657850" cy="3086100"/>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>169445</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 4"/>
+        <xdr:cNvPr id="2" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04541A4C-6DF3-ABFB-463C-094A833E30B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="5657850" cy="3086100"/>
+          <a:off x="609600" y="647700"/>
+          <a:ext cx="5655845" cy="3086100"/>
         </a:xfrm>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>

--- a/XLibur.Tests/Resource/Other/Pictures/ImageShapeZOrder-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/Pictures/ImageShapeZOrder-Output.xlsx
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -112,7 +112,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="正方形/長方形 3">
+        <xdr:cNvPr id="2" name="正方形/長方形 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{810E8613-0B24-485B-9C84-B26EB643DED1}"/>
@@ -176,7 +176,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 4">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04541A4C-6DF3-ABFB-463C-094A833E30B2}"/>
@@ -226,7 +226,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 3">
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F3F4621-BFAA-B945-7453-739AD8016AD9}"/>
